--- a/001_input/02_market_characterization.xlsx
+++ b/001_input/02_market_characterization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/001_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="11_0FEFC881A94BB305686407648BA328F33CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20835604-8C96-4590-9B10-72B4D72CF65B}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="11_0FEFC881A94BB305686407648BA328F33CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BAAA826-31DF-495F-9CC0-F6D67825068C}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="customer_building_type_count" sheetId="1" r:id="rId1"/>
@@ -1186,16 +1186,16 @@
         <v>13</v>
       </c>
       <c r="D10" s="3">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="3">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F10" s="3">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="3">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1209,16 +1209,16 @@
         <v>13</v>
       </c>
       <c r="D11" s="3">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E11" s="3">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F11" s="3">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="3">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1232,16 +1232,16 @@
         <v>13</v>
       </c>
       <c r="D12" s="3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1255,16 +1255,16 @@
         <v>13</v>
       </c>
       <c r="D13" s="3">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E13" s="3">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1412,12 +1412,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1565,15 +1562,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F24D1065-9B3E-4F3B-A1F3-390BA331B399}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BD392A7-7BA8-4912-9645-25D1BF77DA47}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1597,10 +1598,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BD392A7-7BA8-4912-9645-25D1BF77DA47}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F24D1065-9B3E-4F3B-A1F3-390BA331B399}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>